--- a/data/output/evaluasi_96.xlsx
+++ b/data/output/evaluasi_96.xlsx
@@ -8,12 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="9600" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="9606" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="9602" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="9604" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="9601" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="9603" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="9605" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="9604" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="9601" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="9608" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="9606" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9602" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="9603" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="9605" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9607" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,20 +479,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-7.876315019355717</v>
+        <v>-5.207338287962183</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+          <t>adhb_pklnprt_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -505,20 +507,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.835027721885623</v>
+        <v>-5.208539681220456</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+          <t>adhk_pkp_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -533,20 +535,1112 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.988423548623781</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-7.806603051956588</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.382413719485616</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-22.96979375218067</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-19.48703082184375</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1.964100673189873</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D9" t="n">
+        <v>7.512957406547787</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.354432077565615</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-10.68810845166542</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q2-25 vs y-on-y_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2.404133396979977</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-7.242495990734326</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.330625923138631</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>96</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-4.766232282927139</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>96</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.7266258637385806</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>96</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.522788831481964</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01925655856282343</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>96</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-7.242495990734326</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>96</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.8690502759180899</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>96</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.7266258637385806</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.415879078211296</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.572471528820059</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>96</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4.465342153818429</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q2-25 vs implisit_q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>96</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.436559403926833</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>96</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.679210818022887</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q2-25 vs implisit_q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>96</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.2151365714986714</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>96</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.8465964311220826</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>96</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.147164210502637</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>96</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4.224446350310808</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>96</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-6.344137233187819</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>96</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4.339686653905562</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>96</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.402578923983381</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>96</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1.952528172147907</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>96</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8014277075716539</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25 vs implisit_q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>96</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>17.18090873347509</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q1-25 vs implisit_y-on-y_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>96</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>14.15759616071648</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q2-25 vs implisit_y-on-y_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>96</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>17.78667253396385</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25 vs implisit_y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>96</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2.947873246130182</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>96</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3.059990417050844</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>96</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6.233234517705632</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>96</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2.752398706720678</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>96</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Papua Tengah</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2.507157906610273</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -561,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,449 +1692,477 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2714.89932</v>
+        <v>-1.663362544236781</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pklnprt_q1-25_ril vs adhb_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q2-25_ril vs q-to-q_pklnprt_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-569.74658</v>
+        <v>-0.04130842219784046</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pklnprt_q2-25_ril vs sog_q_pklnprt_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7213648073600563</v>
+        <v>2.160221022366672</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pklnprt_q1-25_ril vs distribusi_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.341408147075228</v>
+        <v>1.854790976310609</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.833144572765245</v>
+        <v>0.03169450960045184</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.262776362751669</v>
+        <v>14.6380428089725</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.341408147075228</v>
+        <v>16.16257377559062</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.833144572765245</v>
+        <v>2.459308905615658</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.262776362751669</v>
+        <v>-0.5575303443893872</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.96955619429805</v>
+        <v>4.327061756775268</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.307034985012453</v>
+        <v>12.59963749688405</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.473023310195464</v>
+        <v>2.429324496941563</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.3822438703959664</v>
+        <v>5.075475949183978</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04855927346836608</v>
+        <v>0.993403321754817</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.6346625324000842</v>
+        <v>9.56532900265999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9606</v>
+        <v>9604</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kabupaten Intan Jaya</t>
+          <t>Kabupaten Nabire</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.65170797937016</v>
+        <v>3.893981508374321</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9604</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Nabire</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.14831696921255</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1055,7 +2177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,11 +2214,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9602</v>
+        <v>9601</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Dogiyai</t>
+          <t>Kabupaten Mimika</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1105,44 +2227,436 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.9014461628365</v>
+        <v>1.519335423043472</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9602</v>
+        <v>9601</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Dogiyai</t>
+          <t>Kabupaten Mimika</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.007105153016846126</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25_ril vs implisit_q-to-q_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.002484902136353911</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D4" t="n">
+        <v>-0.1305833878751038</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02167554397804844</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.333740312208285</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-35.13542815300713</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.51367448342776</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-41.14509070457823</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.373475119982818</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5505384836381638</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.549762113101532</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-10.97852969225054</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.748251411345259</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>20.96651512554772</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9.956880213045959</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9601</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Mimika</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.773515272957874</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1157,7 +2671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1194,281 +2708,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-12038.37222009385</v>
+        <v>-0.1227726728601397</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>sog_q_net_ekspor_q2-25_ril vs sog_q_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-9.48672621232171</v>
+        <v>1.409375300302791</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-7.672963495325841</v>
+        <v>0.9848632737641656</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.709093933711752</v>
+        <v>1.095832140338587</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-7.672963495325841</v>
+        <v>2.431476834446371</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-2.709093933711752</v>
+        <v>-5.174138801785631</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.5243197531730961</v>
+        <v>-1.203502716554034</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.2506504535420452</v>
+        <v>1.88963957147987</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9604</v>
+        <v>9608</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kabupaten Nabire</t>
+          <t>Kabupaten Puncak Jaya</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2114645595113311</v>
+        <v>3.474310763370842</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9604</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kabupaten Nabire</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.3826106212027953</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1483,7 +2969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1520,11 +3006,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9601</v>
+        <v>9606</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Mimika</t>
+          <t>Kabupaten Intan Jaya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1533,44 +3019,268 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-5.55112256464536</v>
+        <v>2.021358671065256</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9601</v>
+        <v>9606</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Mimika</t>
+          <t>Kabupaten Intan Jaya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01076074112424304</v>
+        <v>1.991063549220256</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.84404914481072</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.760124245685541</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.508674610639484</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.33834196535036</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.122506031946833</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2887001848171877</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1488453346249139</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9606</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Intan Jaya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.350094212811302</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1585,7 +3295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,113 +3332,281 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9603</v>
+        <v>9602</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Deiyai</t>
+          <t>Kabupaten Dogiyai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.191589274857963</v>
+        <v>1.31260626158976</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9603</v>
+        <v>9602</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Deiyai</t>
+          <t>Kabupaten Dogiyai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.191589274857963</v>
+        <v>0.04231296933108685</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9603</v>
+        <v>9602</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Deiyai</t>
+          <t>Kabupaten Dogiyai</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3042891917407689</v>
+        <v>0.5792157379849509</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9603</v>
+        <v>9602</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Deiyai</t>
+          <t>Kabupaten Dogiyai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.005204224217489371</v>
+        <v>-0.2153494130878549</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7469540938303573</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.91573642786906</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2469825328489279</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0437397891893077</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.541286442662311</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9602</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Dogiyai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.069874289325587</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1743,7 +3621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1780,6 +3658,332 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.809465359203008</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4475170590113342</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.27592221277655</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9522707761363394</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2543718286849385</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.742620618863191</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2291923384527768</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2549733468569962</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.590081319053247</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9603</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Deiyai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.898469122796934</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>9605</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1789,20 +3993,458 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.371365501791361</v>
+        <v>1.09116912054474</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.093546386762926</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.571776345711231</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.475759218514126</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.684974101877103</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.000375532736117</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1310425082389818</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.990588497433418</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9605</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Paniai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.231020533352699</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.246435754100215</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.891562700770838</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.144459894779071</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.630954888064059</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1217885145176992</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9607</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Puncak</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.313585599383553</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_96.xlsx
+++ b/data/output/evaluasi_96.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
